--- a/Decks/Littles.xlsx
+++ b/Decks/Littles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB61B3E9-EED0-4EE9-823B-55A0AAC31695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E082106E-B7B5-4889-823E-7B3176BAD65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Littles" sheetId="1" r:id="rId1"/>
@@ -353,9 +353,6 @@
     <t>Elas il-Kor, Sadistic Pilgrim</t>
   </si>
   <si>
-    <t>Last Price</t>
-  </si>
-  <si>
     <t>Sivriss, Nightmare Speaker</t>
   </si>
   <si>
@@ -383,19 +380,22 @@
     <t>Brazen Cannonade</t>
   </si>
   <si>
-    <t>Captain Claws</t>
-  </si>
-  <si>
-    <t>Skynight Vanguard</t>
-  </si>
-  <si>
-    <t>Winspdrinker Vampire</t>
-  </si>
-  <si>
     <t>Moogles' Valor</t>
   </si>
   <si>
     <t>Lorehold Charm</t>
+  </si>
+  <si>
+    <t>Skyknight Vanguard</t>
+  </si>
+  <si>
+    <t>Captain's Claws</t>
+  </si>
+  <si>
+    <t>Wispdrinker Vampire</t>
+  </si>
+  <si>
+    <t>Ultimate Price</t>
   </si>
 </sst>
 </file>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,10 +1521,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>40</v>
@@ -1649,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>85</v>
@@ -1744,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>88</v>
@@ -1948,7 +1948,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>97</v>
@@ -2024,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>84</v>
@@ -2069,10 +2069,10 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F83"/>
     </row>
@@ -2116,7 +2116,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>86</v>
@@ -2243,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>89</v>
@@ -2321,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>65</v>
@@ -2352,10 +2352,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Littles.xlsx
+++ b/Decks/Littles.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E082106E-B7B5-4889-823E-7B3176BAD65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D811E5-7127-4EAE-9A52-840EF72E6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Littles" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="119">
   <si>
     <t>Função</t>
   </si>
@@ -360,9 +360,6 @@
   </si>
   <si>
     <t>Bontu's Monument</t>
-  </si>
-  <si>
-    <t>Ogre Slumlord</t>
   </si>
   <si>
     <t>Riveteers Overlook</t>
@@ -992,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
@@ -1443,10 +1440,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,10 +1518,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1633,7 +1630,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>40</v>
@@ -1649,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>85</v>
@@ -1744,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>88</v>
@@ -1851,10 +1848,10 @@
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>116</v>
+        <v>37</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>37</v>
@@ -2116,7 +2113,7 @@
         <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>86</v>
@@ -2243,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2258,7 +2255,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>89</v>
@@ -2321,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>65</v>
@@ -2352,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Littles.xlsx
+++ b/Decks/Littles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D811E5-7127-4EAE-9A52-840EF72E6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE8CE3E-32C6-4223-AFE8-D8B3D03CC0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
   <si>
     <t>Função</t>
   </si>
@@ -185,9 +185,6 @@
     <t>Kinscaer Sentry</t>
   </si>
   <si>
-    <t>Rabble Rousing</t>
-  </si>
-  <si>
     <t>Oketra's Monument</t>
   </si>
   <si>
@@ -357,9 +354,6 @@
   </si>
   <si>
     <t>Powerbalance</t>
-  </si>
-  <si>
-    <t>Bontu's Monument</t>
   </si>
   <si>
     <t>Riveteers Overlook</t>
@@ -917,7 +911,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -959,10 +953,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -989,7 +983,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
@@ -1364,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1379,10 +1373,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1440,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1470,10 +1464,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F45"/>
     </row>
@@ -1486,10 +1480,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F46"/>
     </row>
@@ -1502,10 +1496,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F47"/>
     </row>
@@ -1518,10 +1512,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1614,7 +1608,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>38</v>
@@ -1630,7 +1624,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>40</v>
@@ -1646,10 +1640,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F56"/>
     </row>
@@ -1665,7 +1659,7 @@
         <v>45</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F57"/>
     </row>
@@ -1678,10 +1672,10 @@
         <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F58"/>
     </row>
@@ -1710,7 +1704,7 @@
         <v>1</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>39</v>
@@ -1725,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>41</v>
@@ -1741,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F62"/>
     </row>
@@ -1773,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>44</v>
@@ -1786,13 +1780,13 @@
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>72</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E65" s="4"/>
       <c r="F65"/>
@@ -1806,10 +1800,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1821,10 +1815,10 @@
         <v>1</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1836,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1883,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1929,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F74" s="4"/>
     </row>
@@ -1942,417 +1936,417 @@
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B76" s="5" t="b">
         <f>C76&lt;&gt;D76</f>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B77" s="5" t="b">
         <f>C77&lt;&gt;D77</f>
         <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F77"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>50</v>
+      </c>
+      <c r="B81" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C81" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B81" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="D81" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F83"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F86"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B90" s="5" t="b">
         <f>C90&lt;&gt;D90</f>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F91"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D93" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F96"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>61</v>
+      </c>
+      <c r="B97" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B97" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Littles.xlsx
+++ b/Decks/Littles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FE8CE3E-32C6-4223-AFE8-D8B3D03CC0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8229B1FC-020C-4133-9597-9241CEE92271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="113">
   <si>
     <t>Função</t>
   </si>
@@ -281,15 +281,9 @@
     <t>Sulfurous Springs</t>
   </si>
   <si>
-    <t>Braids, Arisen Nightmare</t>
-  </si>
-  <si>
     <t>Iroas, God of Victory</t>
   </si>
   <si>
-    <t>Legion Loyalist</t>
-  </si>
-  <si>
     <t>Ocelot Pride</t>
   </si>
   <si>
@@ -317,9 +311,6 @@
     <t>Thunder of Unity</t>
   </si>
   <si>
-    <t>Warren Soultrader</t>
-  </si>
-  <si>
     <t>Garna, Bloodfist of Keld</t>
   </si>
   <si>
@@ -353,9 +344,6 @@
     <t>Sivriss, Nightmare Speaker</t>
   </si>
   <si>
-    <t>Powerbalance</t>
-  </si>
-  <si>
     <t>Riveteers Overlook</t>
   </si>
   <si>
@@ -371,9 +359,6 @@
     <t>Brazen Cannonade</t>
   </si>
   <si>
-    <t>Moogles' Valor</t>
-  </si>
-  <si>
     <t>Lorehold Charm</t>
   </si>
   <si>
@@ -383,10 +368,13 @@
     <t>Captain's Claws</t>
   </si>
   <si>
-    <t>Wispdrinker Vampire</t>
-  </si>
-  <si>
     <t>Ultimate Price</t>
+  </si>
+  <si>
+    <t>Ares, God of War</t>
+  </si>
+  <si>
+    <t>Arnyn, Deathbloom Botanist</t>
   </si>
 </sst>
 </file>
@@ -829,7 +817,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="b">
-        <f t="shared" ref="B3:B64" si="0">C3&lt;&gt;D3</f>
+        <f t="shared" ref="B3:B66" si="0">C3&lt;&gt;D3</f>
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -983,7 +971,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
@@ -1358,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1373,10 +1361,10 @@
         <v>1</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1434,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1460,14 +1448,14 @@
         <v>23</v>
       </c>
       <c r="B45" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C45&lt;&gt;D45</f>
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F45"/>
     </row>
@@ -1480,10 +1468,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F46"/>
     </row>
@@ -1496,26 +1484,26 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="F48"/>
     </row>
@@ -1528,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F49"/>
     </row>
@@ -1544,10 +1532,10 @@
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F50"/>
     </row>
@@ -1560,10 +1548,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F51"/>
     </row>
@@ -1576,26 +1564,26 @@
         <v>0</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F53"/>
     </row>
@@ -1608,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F54"/>
     </row>
@@ -1624,10 +1612,10 @@
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="F55"/>
     </row>
@@ -1640,10 +1628,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F56"/>
     </row>
@@ -1656,10 +1644,10 @@
         <v>1</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="F57"/>
     </row>
@@ -1672,12 +1660,12 @@
         <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F58"/>
+        <v>42</v>
+      </c>
+      <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -1685,46 +1673,45 @@
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F59" s="4"/>
+        <v>39</v>
+      </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>35</v>
       </c>
       <c r="B60" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>C60&lt;&gt;D60</f>
+        <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>39</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D60" t="s">
+        <v>45</v>
+      </c>
+      <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>35</v>
       </c>
       <c r="B61" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
+        <f>C61&lt;&gt;D61</f>
+        <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F61"/>
+        <v>108</v>
+      </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -1735,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="F62"/>
     </row>
@@ -1747,14 +1734,14 @@
         <v>35</v>
       </c>
       <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C63&lt;&gt;D63</f>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="F63"/>
     </row>
@@ -1767,10 +1754,10 @@
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="F64"/>
     </row>
@@ -1779,16 +1766,15 @@
         <v>35</v>
       </c>
       <c r="B65" s="5" t="b">
-        <f t="shared" ref="B65:B101" si="1">C65&lt;&gt;D65</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E65" s="4"/>
+        <v>43</v>
+      </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1796,30 +1782,33 @@
         <v>35</v>
       </c>
       <c r="B66" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>89</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="F66"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>35</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f>C67&lt;&gt;D67</f>
-        <v>1</v>
+        <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
+        <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>86</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -1829,11 +1818,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C68" t="s">
-        <v>78</v>
+      <c r="C68" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1841,16 +1830,15 @@
         <v>35</v>
       </c>
       <c r="B69" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C69&lt;&gt;D69</f>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E69" s="4"/>
+        <v>84</v>
+      </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
@@ -1860,13 +1848,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>46</v>
+      <c r="C70" t="s">
+        <v>78</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="F70" s="4"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
@@ -1877,11 +1864,12 @@
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>97</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="E71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
@@ -1892,11 +1880,12 @@
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
@@ -1907,12 +1896,11 @@
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F73" s="4"/>
+        <v>94</v>
+      </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
@@ -1923,12 +1911,11 @@
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="F74" s="4"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
@@ -1939,42 +1926,43 @@
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>96</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B76" s="5" t="b">
-        <f>C76&lt;&gt;D76</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B77" s="5" t="b">
-        <f>C77&lt;&gt;D77</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F77"/>
+        <v>93</v>
+      </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
@@ -1985,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -1996,29 +1984,30 @@
         <v>50</v>
       </c>
       <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C79&lt;&gt;D79</f>
+        <v>1</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>50</v>
       </c>
       <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C80&lt;&gt;D80</f>
+        <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -2027,13 +2016,13 @@
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -2045,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2060,12 +2049,11 @@
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F83"/>
+        <v>59</v>
+      </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
@@ -2076,11 +2064,12 @@
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>91</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F84"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
@@ -2091,12 +2080,11 @@
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F85" s="4"/>
+        <v>89</v>
+      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -2104,15 +2092,15 @@
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F86"/>
+        <v>100</v>
+      </c>
+      <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
@@ -2120,15 +2108,15 @@
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="F87" s="4"/>
+        <v>83</v>
+      </c>
+      <c r="F87"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
@@ -2139,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F88" s="4"/>
     </row>
@@ -2155,10 +2143,10 @@
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F89" s="4"/>
     </row>
@@ -2167,31 +2155,31 @@
         <v>50</v>
       </c>
       <c r="B90" s="5" t="b">
-        <f>C90&lt;&gt;D90</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>68</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>50</v>
       </c>
       <c r="B91" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F91"/>
+        <v>68</v>
+      </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
@@ -2202,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D92" t="s">
-        <v>102</v>
+        <v>60</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>60</v>
       </c>
       <c r="F92"/>
     </row>
@@ -2234,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -2249,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F95"/>
     </row>
@@ -2265,10 +2253,10 @@
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F96"/>
     </row>
@@ -2312,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>64</v>
@@ -2343,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Littles.xlsx
+++ b/Decks/Littles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8229B1FC-020C-4133-9597-9241CEE92271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551DBBC1-A280-49C9-B934-88B9E6F75391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F75D263A-00FE-40E8-A865-C2160008CFD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Littles" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="112">
   <si>
     <t>Função</t>
   </si>
@@ -116,15 +116,9 @@
     <t>Morbid Opportunist</t>
   </si>
   <si>
-    <t>Teysa, Opulent Oligarch</t>
-  </si>
-  <si>
     <t>Zurgo Stormrender</t>
   </si>
   <si>
-    <t>Aurelia, the Law Above</t>
-  </si>
-  <si>
     <t>Attack</t>
   </si>
   <si>
@@ -323,9 +317,6 @@
     <t>Venerated Stormsinger</t>
   </si>
   <si>
-    <t>Sephiroth, Fabled SOLDIER</t>
-  </si>
-  <si>
     <t>Yawgmoth, Thran Physician</t>
   </si>
   <si>
@@ -335,9 +326,6 @@
     <t>Gix, Yawgmoth Praetor</t>
   </si>
   <si>
-    <t>Redemption Choir</t>
-  </si>
-  <si>
     <t>Elas il-Kor, Sadistic Pilgrim</t>
   </si>
   <si>
@@ -375,6 +363,15 @@
   </si>
   <si>
     <t>Arnyn, Deathbloom Botanist</t>
+  </si>
+  <si>
+    <t>Throne of the God-Pharaoh</t>
+  </si>
+  <si>
+    <t>Idol of Oblivion</t>
+  </si>
+  <si>
+    <t>The Queen of Dale</t>
   </si>
 </sst>
 </file>
@@ -806,10 +803,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -899,7 +896,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -941,10 +938,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -971,7 +968,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>16</v>
@@ -1346,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1358,13 +1355,13 @@
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1387,31 +1384,31 @@
         <v>23</v>
       </c>
       <c r="B41" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C41&lt;&gt;D41</f>
         <v>0</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
       <c r="B42" s="5" t="b">
-        <f>C42&lt;&gt;D42</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="4"/>
+        <v>99</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -1422,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1433,908 +1430,908 @@
         <v>23</v>
       </c>
       <c r="B44" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C44&lt;&gt;D44</f>
         <v>0</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>28</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>23</v>
       </c>
       <c r="B45" s="5" t="b">
-        <f>C45&lt;&gt;D45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F45"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="F46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B47" s="5" t="b">
-        <f t="shared" si="0"/>
+        <f>C47&lt;&gt;D47</f>
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C48" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="D48" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F48"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F49"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F50"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F51"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B52" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>C52&lt;&gt;D52</f>
+        <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F52"/>
+        <v>111</v>
+      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F54"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F55"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F57"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B60" s="5" t="b">
         <f>C60&lt;&gt;D60</f>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D60" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F60"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B61" s="5" t="b">
         <f>C61&lt;&gt;D61</f>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F62"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B63" s="5" t="b">
         <f>C63&lt;&gt;D63</f>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F63"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F64"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F65"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E67" s="4"/>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B69" s="5" t="b">
         <f>C69&lt;&gt;D69</f>
         <v>0</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>37</v>
-      </c>
       <c r="D71" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E71" s="4"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F72" s="4"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B79" s="5" t="b">
         <f>C79&lt;&gt;D79</f>
         <v>1</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F79"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B80" s="5" t="b">
         <f>C80&lt;&gt;D80</f>
         <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F84"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F87"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F92"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D93" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F93"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F95"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F96"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>59</v>
+      </c>
+      <c r="B98" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B98" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="F98"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F99"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
